--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios122.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios122.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,22 +417,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>stage</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>scenario_index</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>node</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
@@ -463,7 +451,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>29.33532722493943</v>
+        <v>29.539999715091</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +467,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>25.08129984698185</v>
+        <v>22.66793131208874</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +483,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>27.65672302500292</v>
+        <v>19.05099152759472</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +499,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>29.76281434795831</v>
+        <v>26.52487535456873</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +515,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>33.14432937371345</v>
+        <v>26.79956539873789</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +531,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>30.33835232982187</v>
+        <v>27.14614932684583</v>
       </c>
     </row>
     <row r="8">
@@ -559,7 +547,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>28.94338140148319</v>
+        <v>29.52297355133235</v>
       </c>
     </row>
     <row r="9">
@@ -575,7 +563,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>24.74095290192442</v>
+        <v>23.06222324339579</v>
       </c>
     </row>
     <row r="10">
@@ -591,7 +579,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>27.26240356216184</v>
+        <v>19.27021915730926</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +595,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>29.5944070178726</v>
+        <v>26.14608851263465</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +611,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>34.01875811467274</v>
+        <v>27.18327714008216</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +627,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>29.54759766508805</v>
+        <v>26.89318302056885</v>
       </c>
     </row>
     <row r="14">
@@ -655,7 +643,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>25.17635653849396</v>
+        <v>26.4218006815297</v>
       </c>
     </row>
     <row r="15">
@@ -671,7 +659,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>24.96487791344012</v>
+        <v>23.57433618391669</v>
       </c>
     </row>
     <row r="16">
@@ -687,7 +675,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>27.87645585637908</v>
+        <v>31.29478231042926</v>
       </c>
     </row>
     <row r="17">
@@ -703,7 +691,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>29.75917248020791</v>
+        <v>27.42170299983783</v>
       </c>
     </row>
     <row r="18">
@@ -719,7 +707,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>31.56542028290011</v>
+        <v>30.42562060773347</v>
       </c>
     </row>
     <row r="19">
@@ -735,7 +723,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>40.58350098274393</v>
+        <v>20.47851571761272</v>
       </c>
     </row>
     <row r="20">
@@ -751,7 +739,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>24.82589886550102</v>
+        <v>26.33623751041223</v>
       </c>
     </row>
     <row r="21">
@@ -767,7 +755,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>25.54653163193078</v>
+        <v>23.97314759768165</v>
       </c>
     </row>
     <row r="22">
@@ -783,7 +771,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>27.80407179950758</v>
+        <v>31.24710171783331</v>
       </c>
     </row>
     <row r="23">
@@ -799,7 +787,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>29.50232304234102</v>
+        <v>27.17082064563153</v>
       </c>
     </row>
     <row r="24">
@@ -815,7 +803,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>31.55951876101038</v>
+        <v>30.06345979949946</v>
       </c>
     </row>
     <row r="25">
@@ -831,7 +819,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>40.75832951721274</v>
+        <v>20.6595946665824</v>
       </c>
     </row>
   </sheetData>

--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios122.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios122.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,22 +429,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>stage</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>scenario_index</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>node</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
@@ -451,7 +463,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>29.539999715091</v>
+        <v>34.32630620080586</v>
       </c>
     </row>
     <row r="3">
@@ -467,7 +479,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.66793131208874</v>
+        <v>29.10568599229899</v>
       </c>
     </row>
     <row r="4">
@@ -483,7 +495,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.05099152759472</v>
+        <v>21.16397019358921</v>
       </c>
     </row>
     <row r="5">
@@ -499,7 +511,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>26.52487535456873</v>
+        <v>29.59492577516087</v>
       </c>
     </row>
     <row r="6">
@@ -515,7 +527,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>26.79956539873789</v>
+        <v>27.05507896518108</v>
       </c>
     </row>
     <row r="7">
@@ -531,7 +543,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>27.14614932684583</v>
+        <v>29.16880157125755</v>
       </c>
     </row>
     <row r="8">
@@ -547,7 +559,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>29.52297355133235</v>
+        <v>34.50595745071039</v>
       </c>
     </row>
     <row r="9">
@@ -563,7 +575,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>23.06222324339579</v>
+        <v>29.56931799462366</v>
       </c>
     </row>
     <row r="10">
@@ -579,7 +591,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>19.27021915730926</v>
+        <v>21.35669277402662</v>
       </c>
     </row>
     <row r="11">
@@ -595,7 +607,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>26.14608851263465</v>
+        <v>30.27206069100041</v>
       </c>
     </row>
     <row r="12">
@@ -611,7 +623,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>27.18327714008216</v>
+        <v>27.00429662427437</v>
       </c>
     </row>
     <row r="13">
@@ -627,7 +639,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>26.89318302056885</v>
+        <v>29.86037306546217</v>
       </c>
     </row>
     <row r="14">
@@ -643,7 +655,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>26.4218006815297</v>
+        <v>32.56239267724177</v>
       </c>
     </row>
     <row r="15">
@@ -659,7 +671,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>23.57433618391669</v>
+        <v>25.48178210623524</v>
       </c>
     </row>
     <row r="16">
@@ -675,7 +687,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>31.29478231042926</v>
+        <v>29.43849963604183</v>
       </c>
     </row>
     <row r="17">
@@ -691,7 +703,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>27.42170299983783</v>
+        <v>29.29645522319228</v>
       </c>
     </row>
     <row r="18">
@@ -707,7 +719,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>30.42562060773347</v>
+        <v>32.39363064879398</v>
       </c>
     </row>
     <row r="19">
@@ -723,7 +735,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>20.47851571761272</v>
+        <v>33.63595089475974</v>
       </c>
     </row>
     <row r="20">
@@ -739,7 +751,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>26.33623751041223</v>
+        <v>32.51306652981767</v>
       </c>
     </row>
     <row r="21">
@@ -755,7 +767,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>23.97314759768165</v>
+        <v>25.68337095629599</v>
       </c>
     </row>
     <row r="22">
@@ -771,7 +783,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>31.24710171783331</v>
+        <v>29.50518508403421</v>
       </c>
     </row>
     <row r="23">
@@ -787,7 +799,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>27.17082064563153</v>
+        <v>28.71412097134611</v>
       </c>
     </row>
     <row r="24">
@@ -803,7 +815,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>30.06345979949946</v>
+        <v>32.32121412977528</v>
       </c>
     </row>
     <row r="25">
@@ -819,7 +831,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>20.6595946665824</v>
+        <v>33.68350835658811</v>
       </c>
     </row>
   </sheetData>

--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios122.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios122.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,22 +417,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>stage</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>scenario_index</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>node</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>price</t>
         </is>

--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios122.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios122.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,22 +429,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>stage</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>scenario_index</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>node</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
@@ -451,7 +463,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>34.32630620080586</v>
+        <v>29.539999715091</v>
       </c>
     </row>
     <row r="3">
@@ -467,7 +479,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>29.10568599229899</v>
+        <v>22.66793131208874</v>
       </c>
     </row>
     <row r="4">
@@ -483,7 +495,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21.16397019358921</v>
+        <v>19.05099152759472</v>
       </c>
     </row>
     <row r="5">
@@ -499,7 +511,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>29.59492577516087</v>
+        <v>26.52487535456873</v>
       </c>
     </row>
     <row r="6">
@@ -515,7 +527,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>27.05507896518108</v>
+        <v>26.79956539873789</v>
       </c>
     </row>
     <row r="7">
@@ -531,7 +543,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>29.16880157125755</v>
+        <v>27.14614932684583</v>
       </c>
     </row>
     <row r="8">
@@ -547,7 +559,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>34.50595745071039</v>
+        <v>29.52297355133235</v>
       </c>
     </row>
     <row r="9">
@@ -563,7 +575,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>29.56931799462366</v>
+        <v>23.06222324339579</v>
       </c>
     </row>
     <row r="10">
@@ -579,7 +591,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>21.35669277402662</v>
+        <v>19.27021915730926</v>
       </c>
     </row>
     <row r="11">
@@ -595,7 +607,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>30.27206069100041</v>
+        <v>26.14608851263465</v>
       </c>
     </row>
     <row r="12">
@@ -611,7 +623,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>27.00429662427437</v>
+        <v>27.18327714008216</v>
       </c>
     </row>
     <row r="13">
@@ -627,7 +639,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>29.86037306546217</v>
+        <v>26.89318302056885</v>
       </c>
     </row>
     <row r="14">
@@ -643,7 +655,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>32.56239267724177</v>
+        <v>26.4218006815297</v>
       </c>
     </row>
     <row r="15">
@@ -659,7 +671,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>25.48178210623524</v>
+        <v>23.57433618391669</v>
       </c>
     </row>
     <row r="16">
@@ -675,7 +687,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>29.43849963604183</v>
+        <v>31.29478231042926</v>
       </c>
     </row>
     <row r="17">
@@ -691,7 +703,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>29.29645522319228</v>
+        <v>27.42170299983783</v>
       </c>
     </row>
     <row r="18">
@@ -707,7 +719,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>32.39363064879398</v>
+        <v>30.42562060773347</v>
       </c>
     </row>
     <row r="19">
@@ -723,7 +735,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>33.63595089475974</v>
+        <v>20.47851571761272</v>
       </c>
     </row>
     <row r="20">
@@ -739,7 +751,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>32.51306652981767</v>
+        <v>26.33623751041223</v>
       </c>
     </row>
     <row r="21">
@@ -755,7 +767,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>25.68337095629599</v>
+        <v>23.97314759768165</v>
       </c>
     </row>
     <row r="22">
@@ -771,7 +783,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>29.50518508403421</v>
+        <v>31.24710171783331</v>
       </c>
     </row>
     <row r="23">
@@ -787,7 +799,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>28.71412097134611</v>
+        <v>27.17082064563153</v>
       </c>
     </row>
     <row r="24">
@@ -803,7 +815,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>32.32121412977528</v>
+        <v>30.06345979949946</v>
       </c>
     </row>
     <row r="25">
@@ -819,7 +831,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>33.68350835658811</v>
+        <v>20.6595946665824</v>
       </c>
     </row>
   </sheetData>
